--- a/data/raw/inventory/Week 15/Tonor/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 15/Tonor/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 15\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB3853-0467-42AE-9330-71CC743044B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1CD440-6573-41BA-8612-57C3F6482F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="147">
   <si>
     <t>SKU</t>
   </si>
@@ -87,9 +87,6 @@
     <t>FBA79111</t>
   </si>
   <si>
-    <t>FBA79263</t>
-  </si>
-  <si>
     <t>FBA77103</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>B0BRKFP94K</t>
   </si>
   <si>
-    <t>B0CYSLCRQS</t>
-  </si>
-  <si>
     <t>B09Z5Q194D</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>B0CQX4K9P5</t>
   </si>
   <si>
-    <t>TONOR</t>
-  </si>
-  <si>
     <t>Amazon</t>
   </si>
   <si>
@@ -372,9 +363,6 @@
     <t>Tonor</t>
   </si>
   <si>
-    <t>MR-01</t>
-  </si>
-  <si>
     <t>Q9</t>
   </si>
   <si>
@@ -423,18 +411,9 @@
     <t>Hand held Mic</t>
   </si>
   <si>
-    <t>Home &amp; Kitchen</t>
-  </si>
-  <si>
-    <t>Cleaning &amp; Vacumming</t>
-  </si>
-  <si>
     <t>USB/XLR Mic</t>
   </si>
   <si>
-    <t>Mite Remover</t>
-  </si>
-  <si>
     <t>Stand</t>
   </si>
   <si>
@@ -496,16 +475,17 @@
   </si>
   <si>
     <t>1p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+K1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,12 +542,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -613,12 +587,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -647,215 +620,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1086,6 +862,140 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1555,19 +1465,19 @@
         <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7">
@@ -1577,281 +1487,281 @@
         <v>10</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7">
-        <v>652</v>
-      </c>
-      <c r="I3" s="10">
-        <v>1026</v>
+        <v>2412</v>
+      </c>
+      <c r="I3" s="8">
+        <v>12</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7">
-        <v>2412</v>
-      </c>
-      <c r="I4" s="8">
-        <v>12</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>116</v>
+        <v>1244</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>102</v>
+      <c r="C5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7">
         <v>1244</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>105</v>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>76</v>
+      <c r="A6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7">
-        <v>1244</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>116</v>
+        <v>1688</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>82</v>
+      <c r="C7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7">
         <v>1688</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>105</v>
+      <c r="I7" s="8">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>75</v>
+      <c r="A8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>82</v>
+        <v>107</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7">
-        <v>1688</v>
+        <v>1280</v>
       </c>
       <c r="I8" s="8">
-        <v>2</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>116</v>
+        <v>11</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>104</v>
+        <v>57</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7">
         <v>1280</v>
       </c>
       <c r="I9" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>104</v>
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7">
@@ -1860,86 +1770,86 @@
       <c r="I10" s="8">
         <v>0</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>105</v>
+      <c r="J10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>59</v>
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7">
-        <v>1280</v>
+        <v>652</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>116</v>
+      <c r="J11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>59</v>
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7">
-        <v>1280</v>
-      </c>
-      <c r="I12" s="10">
-        <v>240</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>120</v>
+        <v>652</v>
+      </c>
+      <c r="I12" s="8">
+        <v>10</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1947,1651 +1857,1649 @@
         <v>14</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>99</v>
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7">
         <v>652</v>
       </c>
       <c r="I13" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>99</v>
+      <c r="A14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7">
-        <v>652</v>
+        <v>12803</v>
       </c>
       <c r="I14" s="8">
-        <v>10</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>99</v>
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7">
-        <v>652</v>
+        <v>2412</v>
       </c>
       <c r="I15" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>109</v>
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>97</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7">
-        <v>12803</v>
+        <v>2412</v>
       </c>
       <c r="I16" s="8">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>116</v>
+        <v>2</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>111</v>
+        <v>107</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>131</v>
-      </c>
+      <c r="G17" s="7"/>
       <c r="H17" s="7">
-        <v>1162</v>
-      </c>
-      <c r="I17" s="10">
-        <v>1002</v>
+        <v>2910</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>120</v>
+        <v>142</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>2412</v>
+        <v>1086</v>
       </c>
       <c r="I18" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>110</v>
+        <v>51</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7">
-        <v>2412</v>
+        <v>1086</v>
       </c>
       <c r="I19" s="8">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7">
-        <v>2910</v>
+        <v>1086</v>
       </c>
       <c r="I20" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>68</v>
+        <v>55</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7">
-        <v>1086</v>
+        <v>603</v>
       </c>
       <c r="I21" s="8">
         <v>8</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>110</v>
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7">
-        <v>1086</v>
+        <v>603</v>
       </c>
       <c r="I22" s="8">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7">
-        <v>1086</v>
+        <v>603</v>
       </c>
       <c r="I23" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>53</v>
+      <c r="A24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>86</v>
+        <v>107</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7">
-        <v>1086</v>
-      </c>
-      <c r="I24" s="10">
-        <v>204</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>120</v>
+        <v>1164</v>
+      </c>
+      <c r="I24" s="8">
+        <v>38</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>85</v>
+        <v>46</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7">
-        <v>603</v>
+        <v>1164</v>
       </c>
       <c r="I25" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>85</v>
+      <c r="A26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7">
-        <v>603</v>
+        <v>1164</v>
       </c>
       <c r="I26" s="8">
-        <v>2</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>105</v>
+        <v>11</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>57</v>
+      <c r="A27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>85</v>
+        <v>107</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7">
-        <v>603</v>
+        <v>845</v>
       </c>
       <c r="I27" s="8">
-        <v>3</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>116</v>
+        <v>20</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>79</v>
+      <c r="A28" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7">
-        <v>1164</v>
+        <v>845</v>
       </c>
       <c r="I28" s="8">
-        <v>38</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>79</v>
+        <v>45</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7">
-        <v>1164</v>
+        <v>1327</v>
       </c>
       <c r="I29" s="8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>48</v>
+      <c r="A30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>79</v>
+        <v>107</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7">
-        <v>1164</v>
-      </c>
-      <c r="I30" s="8">
-        <v>11</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>116</v>
+        <v>1327</v>
+      </c>
+      <c r="I30" s="8"/>
+      <c r="J30" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>115</v>
+      <c r="A31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7">
-        <v>845</v>
+        <v>1327</v>
       </c>
       <c r="I31" s="8">
-        <v>20</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>70</v>
+        <v>5</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>64</v>
+      <c r="A32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7">
-        <v>845</v>
+        <v>2412</v>
       </c>
       <c r="I32" s="8">
-        <v>48</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>88</v>
+        <v>52</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7">
-        <v>1327</v>
-      </c>
-      <c r="I33" s="8">
-        <v>15</v>
-      </c>
+        <v>2412</v>
+      </c>
+      <c r="I33" s="8"/>
       <c r="J33" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>88</v>
+      <c r="A34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7">
-        <v>1327</v>
-      </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>105</v>
+        <v>2412</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>47</v>
+      <c r="A35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>88</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7">
-        <v>1327</v>
+        <v>3015</v>
       </c>
       <c r="I35" s="8">
-        <v>5</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>47</v>
+      <c r="A36" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7">
-        <v>1327</v>
-      </c>
-      <c r="I36" s="15">
-        <v>30</v>
-      </c>
-      <c r="J36" s="9" t="s">
+        <v>3015</v>
+      </c>
+      <c r="I36" s="8"/>
+      <c r="J36" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="K36" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7">
-        <v>2412</v>
+        <v>3015</v>
       </c>
       <c r="I37" s="8">
-        <v>9</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>70</v>
+        <v>6</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>97</v>
+        <v>48</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7">
-        <v>2412</v>
-      </c>
-      <c r="I38" s="8"/>
+        <v>4423</v>
+      </c>
+      <c r="I38" s="8">
+        <v>9</v>
+      </c>
       <c r="J38" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>54</v>
+      <c r="A39" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>97</v>
+        <v>107</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7">
-        <v>2412</v>
+        <v>4423</v>
       </c>
       <c r="I39" s="8">
-        <v>0</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>116</v>
+        <v>1</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>91</v>
+      <c r="A40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7">
-        <v>3015</v>
+        <v>4423</v>
       </c>
       <c r="I40" s="8">
-        <v>4</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>91</v>
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7">
-        <v>3015</v>
-      </c>
-      <c r="I41" s="8"/>
+        <v>1327</v>
+      </c>
+      <c r="I41" s="8">
+        <v>0</v>
+      </c>
       <c r="J41" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>46</v>
+      <c r="A42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>91</v>
+        <v>107</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7">
-        <v>3015</v>
+        <v>1327</v>
       </c>
       <c r="I42" s="8">
-        <v>6</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>116</v>
+        <v>35</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>103</v>
+        <v>40</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7">
-        <v>4423</v>
+        <v>1327</v>
       </c>
       <c r="I43" s="8">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>103</v>
+      <c r="A44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7">
-        <v>4423</v>
+        <v>1327</v>
       </c>
       <c r="I44" s="8">
-        <v>1</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>105</v>
+        <v>279</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>50</v>
+      <c r="A45" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7">
-        <v>4423</v>
+        <v>1568</v>
       </c>
       <c r="I45" s="8">
-        <v>0</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7">
-        <v>4423</v>
-      </c>
-      <c r="I46" s="15">
-        <v>80</v>
+        <v>1568</v>
+      </c>
+      <c r="I46" s="8">
+        <v>0</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>120</v>
+        <v>142</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7">
-        <v>1327</v>
+        <v>1448</v>
       </c>
       <c r="I47" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>93</v>
+        <v>58</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7">
-        <v>1327</v>
+        <v>1448</v>
       </c>
       <c r="I48" s="8">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>93</v>
+      <c r="A49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7">
-        <v>1327</v>
+        <v>1448</v>
       </c>
       <c r="I49" s="8">
-        <v>27</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>105</v>
+        <v>36</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>41</v>
+      <c r="A50" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D50" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>93</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7">
-        <v>1327</v>
+        <v>1749</v>
       </c>
       <c r="I50" s="8">
-        <v>279</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>116</v>
+        <v>5</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>110</v>
+        <v>59</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7">
-        <v>1568</v>
+        <v>1749</v>
       </c>
       <c r="I51" s="8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7">
-        <v>1568</v>
+        <v>1749</v>
       </c>
       <c r="I52" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I53" s="8">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>110</v>
+        <v>53</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I54" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>60</v>
+      <c r="A55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>78</v>
+        <v>107</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I55" s="8">
-        <v>36</v>
+        <v>1206</v>
+      </c>
+      <c r="I55" s="10">
+        <v>20</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>96</v>
+        <v>26</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7">
-        <v>1749</v>
+        <v>1206</v>
       </c>
       <c r="I56" s="8">
-        <v>5</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>70</v>
+        <v>3</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>96</v>
+      <c r="A57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7">
-        <v>1749</v>
+        <v>1206</v>
       </c>
       <c r="I57" s="8">
-        <v>4</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>105</v>
+        <v>5</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>61</v>
+      <c r="A58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>96</v>
+        <v>107</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7">
-        <v>1749</v>
+        <v>1689</v>
       </c>
       <c r="I58" s="8">
-        <v>10</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3599,1767 +3507,1677 @@
         <v>27</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>92</v>
+        <v>54</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7">
-        <v>1206</v>
+        <v>1689</v>
       </c>
       <c r="I59" s="8">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>92</v>
+      <c r="B60" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7">
-        <v>1206</v>
+        <v>1689</v>
       </c>
       <c r="I60" s="8">
-        <v>5</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>105</v>
+        <v>195</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="12" t="s">
-        <v>27</v>
+      <c r="A61" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>92</v>
+        <v>49</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7">
-        <v>1206</v>
-      </c>
-      <c r="I61" s="12">
-        <v>20</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K61" s="13" t="s">
-        <v>116</v>
+        <v>1930</v>
+      </c>
+      <c r="I61" s="8">
+        <v>1</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>110</v>
+        <v>22</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7">
-        <v>1206</v>
+        <v>1930</v>
       </c>
       <c r="I62" s="8">
-        <v>3</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K62" s="13" t="s">
-        <v>118</v>
+        <v>2</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7">
-        <v>1206</v>
+        <v>1930</v>
       </c>
       <c r="I63" s="8">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7">
-        <v>1689</v>
+        <v>1930</v>
       </c>
       <c r="I64" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>110</v>
+        <v>50</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7">
-        <v>1689</v>
+        <v>1930</v>
       </c>
       <c r="I65" s="8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7">
-        <v>1689</v>
+        <v>1930</v>
       </c>
       <c r="I66" s="8">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>89</v>
+        <v>39</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I68" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>51</v>
+      <c r="A69" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I69" s="8">
-        <v>13</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>116</v>
+        <v>41</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D70" s="7" t="s">
+      <c r="A70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I70" s="8">
-        <v>12</v>
-      </c>
-      <c r="J70" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K70" s="7" t="s">
-        <v>70</v>
+        <v>358</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>110</v>
+        <v>12</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>84</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I71" s="8">
-        <v>9</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>105</v>
+        <v>2</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>52</v>
+      <c r="A72" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>84</v>
+        <v>107</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7">
-        <v>1930</v>
-      </c>
-      <c r="I72" s="8">
-        <v>52</v>
+        <v>1086</v>
+      </c>
+      <c r="I72" s="10">
+        <v>30</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I73" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>87</v>
+        <v>56</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I74" s="8">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>110</v>
+        <v>29</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I75" s="8">
-        <v>41</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K75" s="7" t="s">
-        <v>105</v>
+        <v>4</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>87</v>
+        <v>107</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I76" s="8">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>87</v>
+        <v>38</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7">
-        <v>1206</v>
+        <v>823</v>
       </c>
       <c r="I77" s="8">
-        <v>2</v>
-      </c>
-      <c r="J77" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K77" s="13" t="s">
-        <v>118</v>
+        <v>3</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="12" t="s">
-        <v>30</v>
+      <c r="A78" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>94</v>
+        <v>65</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7">
-        <v>1086</v>
-      </c>
-      <c r="I78" s="12">
-        <v>30</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K78" s="13" t="s">
-        <v>116</v>
+        <v>823</v>
+      </c>
+      <c r="I78" s="8">
+        <v>0</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>94</v>
+      <c r="A79" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7">
-        <v>1086</v>
+        <v>823</v>
       </c>
       <c r="I79" s="8">
-        <v>7</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7">
-        <v>1086</v>
+        <v>921</v>
       </c>
       <c r="I80" s="8">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>110</v>
+        <v>37</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7">
-        <v>1086</v>
+        <v>921</v>
       </c>
       <c r="I81" s="8">
-        <v>4</v>
-      </c>
-      <c r="J81" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K81" s="13" t="s">
-        <v>118</v>
+        <v>30</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>94</v>
+        <v>107</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7">
-        <v>1086</v>
+        <v>921</v>
       </c>
       <c r="I82" s="8">
-        <v>357</v>
+        <v>94</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>68</v>
+        <v>42</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>95</v>
       </c>
       <c r="E83" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F83" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7">
-        <v>823</v>
+        <v>2412</v>
       </c>
       <c r="I83" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D84" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>95</v>
       </c>
       <c r="E84" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7">
-        <v>823</v>
+        <v>2412</v>
       </c>
       <c r="I84" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>67</v>
+      <c r="A85" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D85" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" s="8" t="s">
         <v>95</v>
       </c>
       <c r="E85" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7">
-        <v>823</v>
+        <v>2412</v>
       </c>
       <c r="I85" s="8">
-        <v>1</v>
-      </c>
-      <c r="J85" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>77</v>
+      <c r="A86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="E86" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7">
-        <v>921</v>
+        <v>2412</v>
       </c>
       <c r="I86" s="8">
-        <v>39</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>70</v>
+        <v>11</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>77</v>
+        <v>61</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7">
-        <v>921</v>
+        <v>3491</v>
       </c>
       <c r="I87" s="8">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>66</v>
+      <c r="A88" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>77</v>
+        <v>107</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7">
-        <v>921</v>
-      </c>
-      <c r="I88" s="8">
-        <v>94</v>
-      </c>
-      <c r="J88" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>116</v>
+        <v>3491</v>
+      </c>
+      <c r="I88" s="8"/>
+      <c r="J88" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>77</v>
+        <v>107</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7">
-        <v>921</v>
-      </c>
-      <c r="I89" s="10">
-        <v>256</v>
+        <v>3491</v>
+      </c>
+      <c r="I89" s="8">
+        <v>2</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="K89" s="11" t="s">
-        <v>120</v>
+        <v>142</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7">
-        <v>2412</v>
+        <v>1448</v>
       </c>
       <c r="I90" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D91" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7">
-        <v>2412</v>
+        <v>1448</v>
       </c>
       <c r="I91" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D92" s="8" t="s">
+      <c r="A92" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7">
-        <v>2412</v>
+        <v>1448</v>
       </c>
       <c r="I92" s="8">
-        <v>8</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K92" s="7" t="s">
-        <v>105</v>
+        <v>4</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>43</v>
+      <c r="A93" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7">
-        <v>2412</v>
+        <v>965</v>
       </c>
       <c r="I93" s="8">
-        <v>11</v>
-      </c>
-      <c r="J93" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>116</v>
+        <v>63</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>81</v>
+        <v>60</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7">
-        <v>3491</v>
+        <v>965</v>
       </c>
       <c r="I94" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>81</v>
+      <c r="A95" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7">
-        <v>3491</v>
-      </c>
-      <c r="I95" s="8"/>
-      <c r="J95" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K95" s="7" t="s">
-        <v>105</v>
+        <v>965</v>
+      </c>
+      <c r="I95" s="8">
+        <v>20</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B96" s="4" t="s">
+      <c r="A96" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B96" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="E96" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7">
-        <v>3491</v>
+        <v>1397</v>
       </c>
       <c r="I96" s="8">
-        <v>2</v>
-      </c>
-      <c r="J96" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>116</v>
+        <v>7</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>101</v>
+      <c r="A97" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7">
-        <v>1448</v>
+        <v>1397</v>
       </c>
       <c r="I97" s="8">
-        <v>15</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>70</v>
+        <v>8</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I98" s="1">
+        <v>240</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I99" s="1">
+        <v>150</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I100" s="1">
+        <v>204</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1026</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I102" s="1">
+        <v>504</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L102" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I103" s="1">
+        <v>30</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I98" s="8">
-        <v>0</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I99" s="8">
-        <v>4</v>
-      </c>
-      <c r="J99" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K99" s="3" t="s">
+      <c r="B104" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I104" s="1">
+        <v>80</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L99" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I100" s="10">
-        <v>150</v>
-      </c>
-      <c r="J100" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K100" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="L100" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7">
-        <v>965</v>
-      </c>
-      <c r="I101" s="8">
-        <v>63</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K101" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L101" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7">
-        <v>965</v>
-      </c>
-      <c r="I102" s="8">
-        <v>5</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K102" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L102" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7">
-        <v>965</v>
-      </c>
-      <c r="I103" s="8">
-        <v>20</v>
-      </c>
-      <c r="J103" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K103" s="3" t="s">
+      <c r="L104" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I105" s="1">
+        <v>256</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L103" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7">
-        <v>1397</v>
-      </c>
-      <c r="I104" s="8">
-        <v>7</v>
-      </c>
-      <c r="J104" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K104" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L104" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7">
-        <v>1397</v>
-      </c>
-      <c r="I105" s="8">
-        <v>8</v>
-      </c>
-      <c r="J105" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="L105" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L105" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="47" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="856"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18">
-    <cfRule type="duplicateValues" dxfId="46" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="158" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="159" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D11:D14">
+    <cfRule type="duplicateValues" dxfId="41" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="979" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="980" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="981" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="duplicateValues" dxfId="38" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="150" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="151" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="duplicateValues" dxfId="36" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="158" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="159" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="duplicateValues" dxfId="28" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="150" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="151" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="duplicateValues" dxfId="20" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="938" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="939" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="30" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="907" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="989" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="28" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="855" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="855" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="26" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="853" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="853" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A100:A105">
-    <cfRule type="duplicateValues" dxfId="24" priority="930"/>
+  <conditionalFormatting sqref="A93:A97">
+    <cfRule type="duplicateValues" dxfId="6" priority="990"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24 A9:A19">
-    <cfRule type="duplicateValues" dxfId="23" priority="931"/>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="duplicateValues" dxfId="5" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="993" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="995" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="996" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D21">
-    <cfRule type="duplicateValues" dxfId="22" priority="932"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="933"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="934"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="935"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="936"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="937"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="938" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="939" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="duplicateValues" dxfId="14" priority="953"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="954"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="955" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="956" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="957" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D16">
-    <cfRule type="duplicateValues" dxfId="9" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="979" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="980" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="981" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D12">
-    <cfRule type="duplicateValues" dxfId="4" priority="983"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="984" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="986" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D12">
-    <cfRule type="duplicateValues" dxfId="0" priority="987" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A8:A16">
+    <cfRule type="duplicateValues" dxfId="0" priority="997"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
